--- a/artfynd/A 35245-2025 artfynd.xlsx
+++ b/artfynd/A 35245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127120045</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström, Janne Johansson</t>
+          <t>Janne Johansson, Thomas Arnström, Per Muhr</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -793,7 +793,7 @@
         <v>127120046</v>
       </c>
       <c r="B3" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström, Janne Johansson</t>
+          <t>Janne Johansson, Thomas Arnström, Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -908,7 +908,7 @@
         <v>127120225</v>
       </c>
       <c r="B4" t="n">
-        <v>57815</v>
+        <v>57819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35245-2025 artfynd.xlsx
+++ b/artfynd/A 35245-2025 artfynd.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janne Johansson, Thomas Arnström, Per Muhr</t>
+          <t>Per Muhr, Thomas Arnström, Janne Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janne Johansson, Thomas Arnström, Per Muhr</t>
+          <t>Per Muhr, Thomas Arnström, Janne Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 35245-2025 artfynd.xlsx
+++ b/artfynd/A 35245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127120045</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127120046</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127120225</v>
       </c>
       <c r="B4" t="n">
-        <v>57819</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35245-2025 artfynd.xlsx
+++ b/artfynd/A 35245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127120045</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127120046</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127120225</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>57824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35245-2025 artfynd.xlsx
+++ b/artfynd/A 35245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127120045</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127120046</v>
       </c>
       <c r="B3" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127120225</v>
       </c>
       <c r="B4" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35245-2025 artfynd.xlsx
+++ b/artfynd/A 35245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127120045</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127120046</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>58027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127120225</v>
       </c>
       <c r="B4" t="n">
-        <v>57830</v>
+        <v>57815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35245-2025 artfynd.xlsx
+++ b/artfynd/A 35245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127120045</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>127120046</v>
       </c>
       <c r="B3" t="n">
-        <v>58027</v>
+        <v>58042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>127120225</v>
       </c>
       <c r="B4" t="n">
-        <v>57815</v>
+        <v>57830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35245-2025 artfynd.xlsx
+++ b/artfynd/A 35245-2025 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127120045</v>
+        <v>127120046</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -790,27 +790,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127120046</v>
+        <v>127120225</v>
       </c>
       <c r="B3" t="n">
-        <v>58042</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405982</v>
+        <v>406119</v>
       </c>
       <c r="R3" t="n">
-        <v>6252539</v>
+        <v>6252296</v>
       </c>
       <c r="S3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,17 +898,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Muhr, Thomas Arnström, Janne Johansson</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127120225</v>
+        <v>127120045</v>
       </c>
       <c r="B4" t="n">
-        <v>57830</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,26 +916,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406119</v>
+        <v>405982</v>
       </c>
       <c r="R4" t="n">
-        <v>6252296</v>
+        <v>6252539</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Per Muhr, Thomas Arnström, Janne Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 35245-2025 artfynd.xlsx
+++ b/artfynd/A 35245-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127120046</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127120225</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,8 +1032,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127120045</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>